--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_1_R1.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_1_R1.xlsx
@@ -565,10 +565,10 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.4352</v>
+        <v>5.5531</v>
       </c>
       <c r="E2" t="n">
-        <v>3.1462</v>
+        <v>3.2642</v>
       </c>
       <c r="F2" t="n">
         <v>2.2889</v>
@@ -610,10 +610,10 @@
         <v>1.3917</v>
       </c>
       <c r="S2" t="n">
-        <v>0.9278</v>
+        <v>1.0458</v>
       </c>
       <c r="T2" t="n">
-        <v>0.1889</v>
+        <v>0.3068</v>
       </c>
       <c r="U2" t="n">
         <v>0.7389</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.0856</v>
+        <v>4.7918</v>
       </c>
       <c r="E3" t="n">
-        <v>4.059</v>
+        <v>5.034</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0266</v>
+        <v>-0.2422</v>
       </c>
       <c r="G3" t="n">
         <v>5.0673</v>
@@ -688,13 +688,13 @@
         <v>0.9278</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.608</v>
+        <v>0.0982</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.8962</v>
+        <v>0.0788</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2882</v>
+        <v>0.0193</v>
       </c>
       <c r="V3" t="n">
         <v>-0.1418</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>G. PAPAGIANNIS</t>
+          <t>J. LOYD</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.9966</v>
+        <v>2.8142</v>
       </c>
       <c r="E4" t="n">
-        <v>2.2236</v>
+        <v>2.2324</v>
       </c>
       <c r="F4" t="n">
-        <v>1.773</v>
+        <v>0.5818</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.0375</v>
+        <v>3.7104</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.6399</v>
+        <v>0.7527</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6022999999999999</v>
+        <v>2.9577</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.5484</v>
+        <v>4.5792</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0539</v>
+        <v>1.983</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.6022999999999999</v>
+        <v>2.5962</v>
       </c>
       <c r="M4" t="n">
-        <v>0.5109</v>
+        <v>-0.8687</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.6938</v>
+        <v>-1.2303</v>
       </c>
       <c r="O4" t="n">
-        <v>1.2046</v>
+        <v>0.3615</v>
       </c>
       <c r="P4" t="n">
-        <v>0.6959</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-2.3195</v>
       </c>
       <c r="R4" t="n">
-        <v>0.6959</v>
+        <v>2.3195</v>
       </c>
       <c r="S4" t="n">
-        <v>3.3382</v>
+        <v>0.1759</v>
       </c>
       <c r="T4" t="n">
-        <v>2.772</v>
+        <v>-0.0272</v>
       </c>
       <c r="U4" t="n">
-        <v>0.5663</v>
+        <v>0.2032</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>-1.0722</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. LOYD</t>
+          <t>G. PAPAGIANNIS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.5043</v>
+        <v>2.3026</v>
       </c>
       <c r="E5" t="n">
-        <v>2.1578</v>
+        <v>0.7649</v>
       </c>
       <c r="F5" t="n">
-        <v>0.3465</v>
+        <v>1.5377</v>
       </c>
       <c r="G5" t="n">
-        <v>3.7104</v>
+        <v>-0.0375</v>
       </c>
       <c r="H5" t="n">
-        <v>0.7527</v>
+        <v>-0.6399</v>
       </c>
       <c r="I5" t="n">
-        <v>2.9577</v>
+        <v>0.6022999999999999</v>
       </c>
       <c r="J5" t="n">
-        <v>4.5792</v>
+        <v>-0.5484</v>
       </c>
       <c r="K5" t="n">
-        <v>1.983</v>
+        <v>0.0539</v>
       </c>
       <c r="L5" t="n">
-        <v>2.5962</v>
+        <v>-0.6022999999999999</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.8687</v>
+        <v>0.5109</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.2303</v>
+        <v>-0.6938</v>
       </c>
       <c r="O5" t="n">
-        <v>0.3615</v>
+        <v>1.2046</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>0.6959</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.3195</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>2.3195</v>
+        <v>0.6959</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.134</v>
+        <v>1.6443</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.1019</v>
+        <v>1.3133</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.0321</v>
+        <v>0.331</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.0722</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.0722</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.5309</v>
+        <v>2.1508</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.4094</v>
+        <v>-1.26</v>
       </c>
       <c r="F6" t="n">
-        <v>2.9403</v>
+        <v>3.4108</v>
       </c>
       <c r="G6" t="n">
         <v>-1.4222</v>
@@ -922,13 +922,13 @@
         <v>2.5515</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.1344</v>
+        <v>0.4854</v>
       </c>
       <c r="T6" t="n">
-        <v>0.6844</v>
+        <v>0.8338</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.8188</v>
+        <v>-0.3484</v>
       </c>
       <c r="V6" t="n">
         <v>0.5361</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.8875999999999999</v>
+        <v>-0.7609</v>
       </c>
       <c r="E7" t="n">
-        <v>0.5897</v>
+        <v>1.2541</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.4773</v>
+        <v>-2.015</v>
       </c>
       <c r="G7" t="n">
         <v>0.4515</v>
@@ -1000,13 +1000,13 @@
         <v>0.6959</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.3391</v>
+        <v>-0.2124</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.5895</v>
+        <v>0.07489999999999999</v>
       </c>
       <c r="U7" t="n">
-        <v>0.2504</v>
+        <v>-0.2873</v>
       </c>
       <c r="V7" t="n">
         <v>-0.5361</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>C. SWIDER</t>
+          <t>S. LARKIN</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.9353</v>
+        <v>-0.7675</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.0747</v>
+        <v>-0.1297</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.8606</v>
+        <v>-0.6377</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.1896</v>
+        <v>-0.2196</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.3469</v>
+        <v>1.9386</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1573</v>
+        <v>-2.1582</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>0.4955</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>2.2791</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>-1.7836</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.1896</v>
+        <v>-0.7151</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.3469</v>
+        <v>-0.3405</v>
       </c>
       <c r="O8" t="n">
-        <v>0.1573</v>
+        <v>-0.3746</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>-0.232</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-2.3195</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>2.0876</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.2095</v>
+        <v>0.4727</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.0747</v>
+        <v>0.3385</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.1349</v>
+        <v>0.1342</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.5361</v>
+        <v>-0.7886</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.3558</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.5361</v>
+        <v>-2.1444</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>E. OSMANI</t>
+          <t>C. SWIDER</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.2932</v>
+        <v>-0.7837</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.5094</v>
+        <v>0.0433</v>
       </c>
       <c r="F9" t="n">
-        <v>0.2162</v>
+        <v>-0.827</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.1582</v>
+        <v>-0.1896</v>
       </c>
       <c r="H9" t="n">
-        <v>0.9626</v>
+        <v>-0.3469</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.1209</v>
+        <v>0.1573</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.3153</v>
+        <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>1.2708</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.5861</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>0.1571</v>
+        <v>-0.1896</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.3082</v>
+        <v>-0.3469</v>
       </c>
       <c r="O9" t="n">
-        <v>0.4653</v>
+        <v>0.1573</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.6959</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>-3.4793</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>2.7834</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.0448</v>
+        <v>-0.058</v>
       </c>
       <c r="T9" t="n">
-        <v>0.5351</v>
+        <v>0.0433</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.5799</v>
+        <v>-0.1013</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.3943</v>
+        <v>-0.5361</v>
       </c>
       <c r="W9" t="n">
-        <v>1.7501</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-2.1444</v>
+        <v>-0.5361</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>S. LARKIN</t>
+          <t>E. OSMANI</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,64 +1189,64 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.5999</v>
+        <v>-1.2288</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.7942</v>
+        <v>-1.7139</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.8058</v>
+        <v>0.4851</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.2196</v>
+        <v>-0.1582</v>
       </c>
       <c r="H10" t="n">
-        <v>1.9386</v>
+        <v>0.9626</v>
       </c>
       <c r="I10" t="n">
-        <v>-2.1582</v>
+        <v>-1.1209</v>
       </c>
       <c r="J10" t="n">
-        <v>0.4955</v>
+        <v>-0.3153</v>
       </c>
       <c r="K10" t="n">
-        <v>2.2791</v>
+        <v>1.2708</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.7836</v>
+        <v>-1.5861</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.7151</v>
+        <v>0.1571</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.3405</v>
+        <v>-0.3082</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.3746</v>
+        <v>0.4653</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.232</v>
+        <v>-0.6959</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.3195</v>
+        <v>-3.4793</v>
       </c>
       <c r="R10" t="n">
-        <v>2.0876</v>
+        <v>2.7834</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.3598</v>
+        <v>0.0196</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.326</v>
+        <v>0.3306</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.0338</v>
+        <v>-0.311</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.7886</v>
+        <v>-0.3943</v>
       </c>
       <c r="W10" t="n">
-        <v>1.3558</v>
+        <v>1.7501</v>
       </c>
       <c r="X10" t="n">
         <v>-2.1444</v>
@@ -1267,10 +1267,10 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.7386</v>
+        <v>-1.6206</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.2344</v>
+        <v>-1.1165</v>
       </c>
       <c r="F11" t="n">
         <v>-0.5041</v>
@@ -1312,10 +1312,10 @@
         <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.232</v>
+        <v>-0.114</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.0747</v>
+        <v>0.0433</v>
       </c>
       <c r="U11" t="n">
         <v>-0.1573</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.423</v>
+        <v>-5.0293</v>
       </c>
       <c r="E12" t="n">
-        <v>-5.4475</v>
+        <v>-5.9193</v>
       </c>
       <c r="F12" t="n">
-        <v>1.0245</v>
+        <v>0.89</v>
       </c>
       <c r="G12" t="n">
         <v>-1.8566</v>
@@ -1390,13 +1390,13 @@
         <v>0.4639</v>
       </c>
       <c r="S12" t="n">
-        <v>1.6087</v>
+        <v>1.0025</v>
       </c>
       <c r="T12" t="n">
-        <v>1.4233</v>
+        <v>0.9515</v>
       </c>
       <c r="U12" t="n">
-        <v>0.1854</v>
+        <v>0.051</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>6.675000000000002</v>
+        <v>7.421699999999999</v>
       </c>
       <c r="E13" t="n">
-        <v>1.706699999999999</v>
+        <v>2.4535</v>
       </c>
       <c r="F13" t="n">
-        <v>4.9682</v>
+        <v>4.968299999999999</v>
       </c>
       <c r="G13" t="n">
         <v>7.720000000000001</v>
@@ -1438,7 +1438,7 @@
         <v>4.039300000000001</v>
       </c>
       <c r="I13" t="n">
-        <v>3.6804</v>
+        <v>3.680400000000001</v>
       </c>
       <c r="J13" t="n">
         <v>9.1523</v>
@@ -1447,13 +1447,13 @@
         <v>8.316899999999999</v>
       </c>
       <c r="L13" t="n">
-        <v>0.8354000000000008</v>
+        <v>0.8353999999999999</v>
       </c>
       <c r="M13" t="n">
         <v>-1.4321</v>
       </c>
       <c r="N13" t="n">
-        <v>-4.277500000000001</v>
+        <v>-4.2775</v>
       </c>
       <c r="O13" t="n">
         <v>2.8451</v>
@@ -1468,19 +1468,19 @@
         <v>13.9172</v>
       </c>
       <c r="S13" t="n">
-        <v>3.813099999999999</v>
+        <v>4.56</v>
       </c>
       <c r="T13" t="n">
-        <v>3.540699999999999</v>
+        <v>4.2876</v>
       </c>
       <c r="U13" t="n">
-        <v>0.2724</v>
+        <v>0.2723000000000001</v>
       </c>
       <c r="V13" t="n">
         <v>-2.5387</v>
       </c>
       <c r="W13" t="n">
-        <v>5.250299999999999</v>
+        <v>5.2503</v>
       </c>
       <c r="X13" t="n">
         <v>-7.789000000000001</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.3925</v>
+        <v>3.22</v>
       </c>
       <c r="E14" t="n">
-        <v>3.4403</v>
+        <v>2.6147</v>
       </c>
       <c r="F14" t="n">
-        <v>0.9522</v>
+        <v>0.6054</v>
       </c>
       <c r="G14" t="n">
         <v>0.5072</v>
@@ -1546,13 +1546,13 @@
         <v>2.0876</v>
       </c>
       <c r="S14" t="n">
-        <v>1.7436</v>
+        <v>0.5711000000000001</v>
       </c>
       <c r="T14" t="n">
-        <v>0.948</v>
+        <v>0.1223</v>
       </c>
       <c r="U14" t="n">
-        <v>0.7956</v>
+        <v>0.4488</v>
       </c>
       <c r="V14" t="n">
         <v>1.214</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.4012</v>
+        <v>1.9966</v>
       </c>
       <c r="E15" t="n">
-        <v>1.3518</v>
+        <v>0.88</v>
       </c>
       <c r="F15" t="n">
-        <v>1.0494</v>
+        <v>1.1166</v>
       </c>
       <c r="G15" t="n">
         <v>0.5804</v>
@@ -1624,13 +1624,13 @@
         <v>0.9278</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.1792</v>
+        <v>-0.5838</v>
       </c>
       <c r="T15" t="n">
-        <v>0.1889</v>
+        <v>-0.2829</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.3681</v>
+        <v>-0.3009</v>
       </c>
       <c r="V15" t="n">
         <v>1.0722</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.5264</v>
+        <v>1.813</v>
       </c>
       <c r="E16" t="n">
-        <v>1.0229</v>
+        <v>1.3768</v>
       </c>
       <c r="F16" t="n">
-        <v>0.5034</v>
+        <v>0.4362</v>
       </c>
       <c r="G16" t="n">
         <v>0.9607</v>
@@ -1702,13 +1702,13 @@
         <v>1.1598</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.9883999999999999</v>
+        <v>-0.7018</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.3734</v>
+        <v>-0.0196</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.615</v>
+        <v>-0.6822</v>
       </c>
       <c r="V16" t="n">
         <v>0.3943</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>W. RAYMAN</t>
+          <t>R. SORKIN</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.6163999999999999</v>
+        <v>0.9354</v>
       </c>
       <c r="E17" t="n">
-        <v>0.3172</v>
+        <v>2.9271</v>
       </c>
       <c r="F17" t="n">
-        <v>0.2992</v>
+        <v>-1.9917</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.9866</v>
+        <v>-2.2229</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.3409</v>
+        <v>-0.7407</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.6458</v>
+        <v>-1.4822</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.7327</v>
+        <v>0.262</v>
       </c>
       <c r="K17" t="n">
-        <v>0.0168</v>
+        <v>1.6875</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.7495000000000001</v>
+        <v>-1.4255</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.2539</v>
+        <v>-2.4849</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.3577</v>
+        <v>-2.4282</v>
       </c>
       <c r="O17" t="n">
-        <v>0.1038</v>
+        <v>-0.0568</v>
       </c>
       <c r="P17" t="n">
-        <v>0.6959</v>
+        <v>1.6237</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>0.6959</v>
+        <v>1.6237</v>
       </c>
       <c r="S17" t="n">
-        <v>0.9071</v>
+        <v>-0.0736</v>
       </c>
       <c r="T17" t="n">
-        <v>1.0499</v>
+        <v>-0.0154</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.1428</v>
+        <v>-0.0582</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>1.6083</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>2.6805</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>R. SORKIN</t>
+          <t>W. RAYMAN</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.3742</v>
+        <v>0.0602</v>
       </c>
       <c r="E18" t="n">
-        <v>2.6912</v>
+        <v>-0.2726</v>
       </c>
       <c r="F18" t="n">
-        <v>-2.317</v>
+        <v>0.3328</v>
       </c>
       <c r="G18" t="n">
-        <v>-2.2229</v>
+        <v>-0.9866</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.7407</v>
+        <v>-0.3409</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.4822</v>
+        <v>-0.6458</v>
       </c>
       <c r="J18" t="n">
-        <v>0.262</v>
+        <v>-0.7327</v>
       </c>
       <c r="K18" t="n">
-        <v>1.6875</v>
+        <v>0.0168</v>
       </c>
       <c r="L18" t="n">
-        <v>-1.4255</v>
+        <v>-0.7495000000000001</v>
       </c>
       <c r="M18" t="n">
-        <v>-2.4849</v>
+        <v>-0.2539</v>
       </c>
       <c r="N18" t="n">
-        <v>-2.4282</v>
+        <v>-0.3577</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.0568</v>
+        <v>0.1038</v>
       </c>
       <c r="P18" t="n">
-        <v>1.6237</v>
+        <v>0.6959</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.6237</v>
+        <v>0.6959</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.6348</v>
+        <v>0.351</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.2513</v>
+        <v>0.4602</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.3835</v>
+        <v>-0.1092</v>
       </c>
       <c r="V18" t="n">
-        <v>1.6083</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>2.6805</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.0722</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>O. BRISSETT</t>
+          <t>M. SANTOS</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.195</v>
+        <v>-0.2412</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.7633</v>
+        <v>-1.784</v>
       </c>
       <c r="F19" t="n">
-        <v>1.9583</v>
+        <v>1.5428</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.091</v>
+        <v>0.3182</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.2378</v>
+        <v>1.1044</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.8532</v>
+        <v>-0.7862</v>
       </c>
       <c r="J19" t="n">
-        <v>0.042</v>
+        <v>-0.3363</v>
       </c>
       <c r="K19" t="n">
-        <v>0.3634</v>
+        <v>0.3396</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.3213</v>
+        <v>-0.6758999999999999</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.133</v>
+        <v>0.6545</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.6012</v>
+        <v>0.7648</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.5319</v>
+        <v>-0.1103</v>
       </c>
       <c r="P19" t="n">
-        <v>0.6959</v>
+        <v>-0.6959</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.1598</v>
+        <v>-2.3195</v>
       </c>
       <c r="R19" t="n">
-        <v>1.8556</v>
+        <v>1.6237</v>
       </c>
       <c r="S19" t="n">
-        <v>0.7319</v>
+        <v>-0.9357</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.2513</v>
+        <v>-0.2003</v>
       </c>
       <c r="U19" t="n">
-        <v>0.9832</v>
+        <v>-0.7354000000000001</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.1418</v>
+        <v>1.0722</v>
       </c>
       <c r="W19" t="n">
-        <v>-0.3943</v>
+        <v>1.0722</v>
       </c>
       <c r="X19" t="n">
-        <v>0.2525</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>U. TRIFUNOVIC</t>
+          <t>O. BRISSETT</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.858</v>
+        <v>-0.3935</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.2497</v>
+        <v>-1.8813</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.6083</v>
+        <v>1.4878</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.7007</v>
+        <v>-1.091</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.1452</v>
+        <v>-0.2378</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.5555</v>
+        <v>-0.8532</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.175</v>
+        <v>0.042</v>
       </c>
       <c r="K20" t="n">
-        <v>0.5377999999999999</v>
+        <v>0.3634</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.7127</v>
+        <v>-0.3213</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.5256999999999999</v>
+        <v>-1.133</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.6830000000000001</v>
+        <v>-0.6012</v>
       </c>
       <c r="O20" t="n">
-        <v>0.1573</v>
+        <v>-0.5319</v>
       </c>
       <c r="P20" t="n">
-        <v>0.232</v>
+        <v>0.6959</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R20" t="n">
-        <v>0.232</v>
+        <v>1.8556</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.3892</v>
+        <v>0.1434</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.0747</v>
+        <v>-0.3692</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.3145</v>
+        <v>0.5127</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>-0.1418</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>-0.3943</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>0.2525</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>M. SANTOS</t>
+          <t>U. TRIFUNOVIC</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,64 +2047,64 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.9819</v>
+        <v>-0.5827</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.2558</v>
+        <v>-0.1317</v>
       </c>
       <c r="F21" t="n">
-        <v>1.2739</v>
+        <v>-0.451</v>
       </c>
       <c r="G21" t="n">
-        <v>0.3182</v>
+        <v>-0.7007</v>
       </c>
       <c r="H21" t="n">
-        <v>1.1044</v>
+        <v>-0.1452</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.7862</v>
+        <v>-0.5555</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.3363</v>
+        <v>-0.175</v>
       </c>
       <c r="K21" t="n">
-        <v>0.3396</v>
+        <v>0.5377999999999999</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.6758999999999999</v>
+        <v>-0.7127</v>
       </c>
       <c r="M21" t="n">
-        <v>0.6545</v>
+        <v>-0.5256999999999999</v>
       </c>
       <c r="N21" t="n">
-        <v>0.7648</v>
+        <v>-0.6830000000000001</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.1103</v>
+        <v>0.1573</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.6959</v>
+        <v>0.232</v>
       </c>
       <c r="Q21" t="n">
-        <v>-2.3195</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.6237</v>
+        <v>0.232</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.6764</v>
+        <v>-0.114</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.6721</v>
+        <v>0.0433</v>
       </c>
       <c r="U21" t="n">
-        <v>-1.0042</v>
+        <v>-0.1573</v>
       </c>
       <c r="V21" t="n">
-        <v>1.0722</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>1.0722</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
         <v>0</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.934</v>
+        <v>-0.8509</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.6465</v>
+        <v>-0.0568</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.2875</v>
+        <v>-0.7942</v>
       </c>
       <c r="G22" t="n">
         <v>3.5427</v>
@@ -2170,13 +2170,13 @@
         <v>1.8556</v>
       </c>
       <c r="S22" t="n">
-        <v>-2.2448</v>
+        <v>-1.1617</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.9709</v>
+        <v>-0.3811</v>
       </c>
       <c r="U22" t="n">
-        <v>-1.274</v>
+        <v>-0.7806</v>
       </c>
       <c r="V22" t="n">
         <v>-1.6083</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.1812</v>
+        <v>-2.1311</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.58</v>
+        <v>-2.6979</v>
       </c>
       <c r="F23" t="n">
-        <v>0.3988</v>
+        <v>0.5668</v>
       </c>
       <c r="G23" t="n">
         <v>-2.9302</v>
@@ -2248,13 +2248,13 @@
         <v>1.6237</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.8746</v>
+        <v>-0.8246</v>
       </c>
       <c r="T23" t="n">
-        <v>0.0395</v>
+        <v>-0.0784</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.9142</v>
+        <v>-0.7461</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.6032</v>
+        <v>-3.6875</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.4285</v>
+        <v>-2.6028</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.1747</v>
+        <v>-1.0846</v>
       </c>
       <c r="G24" t="n">
         <v>-0.5326</v>
@@ -2326,13 +2326,13 @@
         <v>1.6237</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.0552</v>
+        <v>-0.1395</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.8883</v>
+        <v>-0.0626</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.1669</v>
+        <v>-0.0769</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-5.6224</v>
+        <v>-6.027</v>
       </c>
       <c r="E25" t="n">
-        <v>-3.4041</v>
+        <v>-3.8759</v>
       </c>
       <c r="F25" t="n">
-        <v>-2.2182</v>
+        <v>-2.151</v>
       </c>
       <c r="G25" t="n">
         <v>-5.1652</v>
@@ -2404,13 +2404,13 @@
         <v>0.9278</v>
       </c>
       <c r="S25" t="n">
-        <v>0.847</v>
+        <v>0.4424</v>
       </c>
       <c r="T25" t="n">
-        <v>0.9831</v>
+        <v>0.5113</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.1362</v>
+        <v>-0.06900000000000001</v>
       </c>
       <c r="V25" t="n">
         <v>-1.0722</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-6.675000000000001</v>
+        <v>-5.8887</v>
       </c>
       <c r="E26" t="n">
-        <v>-5.504500000000002</v>
+        <v>-5.5044</v>
       </c>
       <c r="F26" t="n">
-        <v>-1.1705</v>
+        <v>-0.3841000000000001</v>
       </c>
       <c r="G26" t="n">
         <v>-7.72</v>
@@ -2470,10 +2470,10 @@
         <v>-8.3171</v>
       </c>
       <c r="O26" t="n">
-        <v>-0.8353</v>
+        <v>-0.8353000000000002</v>
       </c>
       <c r="P26" t="n">
-        <v>2.319599999999999</v>
+        <v>2.3196</v>
       </c>
       <c r="Q26" t="n">
         <v>-13.9172</v>
@@ -2482,16 +2482,16 @@
         <v>16.2369</v>
       </c>
       <c r="S26" t="n">
-        <v>-3.813</v>
+        <v>-3.0268</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.2726000000000001</v>
+        <v>-0.2724</v>
       </c>
       <c r="U26" t="n">
-        <v>-3.5406</v>
+        <v>-2.7543</v>
       </c>
       <c r="V26" t="n">
-        <v>2.538700000000001</v>
+        <v>2.5387</v>
       </c>
       <c r="W26" t="n">
         <v>7.2529</v>
